--- a/samples/review_stats_demo_japanese/aggregate_outputs/集計結果サマリー.xlsx
+++ b/samples/review_stats_demo_japanese/aggregate_outputs/集計結果サマリー.xlsx
@@ -17,12 +17,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品質警告" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'案件別サマリー'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'工程別指標'!$A$1:$S$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'工程横断'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'作業担当者別'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'レビュー担当者別'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'横断集計'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'案件別サマリー'!$A$1:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'工程別指標'!$A$1:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'工程横断'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'作業担当者別'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'レビュー担当者別'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'横断集計'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'指摘一覧'!$A$1:$S$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'品質警告'!$A$1:$G$1</definedName>
   </definedNames>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,12 +450,13 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,55 +477,60 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>指摘件数</t>
+          <t>全指摘件数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>表示対象指摘件数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>指標対象指摘件数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>軽微指摘件数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>不良指摘件数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>流出率</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>未対応指摘件数</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>コード変更ステップ数</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>外部仕様書ページ数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>内部仕様書ページ数</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>テスト仕様書ページ数</t>
         </is>
@@ -558,45 +564,50 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>420.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
@@ -630,45 +641,50 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>760.0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>14.0</t>
         </is>
@@ -702,52 +718,57 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.2857142857142857</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>280.0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -758,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -771,15 +792,16 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -800,80 +822,85 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>指摘件数</t>
+          <t>全指摘件数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>表示対象指摘件数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>指標対象指摘件数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>軽微指摘件数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>不良指摘件数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>累積検出不良件数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>除去可能不良件数</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>対象工程までに除去した不良件数</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>対象工程から流出した不良件数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>密度分母</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分母値</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>指摘密度</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>1000文字あたり指摘密度</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>不良除去率</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>流出率</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>未対応指摘件数</t>
         </is>
@@ -927,14 +954,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
@@ -942,31 +969,36 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.05555555555555555</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1000,66 +1032,71 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.16666666666666666</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.6666666666666666</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.3333333333333333</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1103,56 +1140,61 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>変更ステップ数(KLOC換算)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>420.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2.380952380952381</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1186,66 +1228,71 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.1111111111111111</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1264,7 +1311,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>後工程/流出</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1279,62 +1326,67 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>最終把握不良件数</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>対象数</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1368,12 +1420,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1383,12 +1435,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1398,36 +1450,41 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.09090909090909091</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1461,66 +1518,71 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.13333333333333333</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1554,66 +1616,71 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>変更ステップ数(KLOC換算)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>760.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2.6315789473684212</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1657,56 +1724,61 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>14.0</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.07142857142857142</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1725,7 +1797,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>後工程/流出</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1750,52 +1822,57 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>最終把握不良件数</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>対象数</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1844,12 +1921,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1859,36 +1936,41 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.125</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1922,66 +2004,71 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>0.1111111111111111</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>0.6666666666666666</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>0.3333333333333333</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2015,66 +2102,71 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>変更ステップ数(KLOC換算)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>280.0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>7.142857142857143</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2108,66 +2200,71 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>レビュー対象ページ数</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>0.2857142857142857</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>0.7142857142857143</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>0.2857142857142857</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2186,7 +2283,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>後工程/流出</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2201,69 +2298,74 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>最終把握不良件数</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>対象数</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0.7142857142857143</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.2857142857142857</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S16"/>
+  <autoFilter ref="A1:T16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2274,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2285,6 +2387,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2300,30 +2403,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>指摘件数</t>
+          <t>全指摘件数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>表示対象指摘件数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>指標対象指摘件数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>軽微指摘件数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>不良指摘件数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未対応指摘件数</t>
         </is>
@@ -2352,20 +2460,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2394,20 +2507,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2426,30 +2544,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2478,20 +2601,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2520,69 +2648,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>工程</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>後工程</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2593,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2604,6 +2695,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2619,30 +2711,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>指摘件数</t>
+          <t>全指摘件数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>表示対象指摘件数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>指標対象指摘件数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>軽微指摘件数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>不良指摘件数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未対応指摘件数</t>
         </is>
@@ -2671,20 +2768,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2713,27 +2815,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2744,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2755,6 +2862,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2770,30 +2878,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>指摘件数</t>
+          <t>全指摘件数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>表示対象指摘件数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>指標対象指摘件数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>軽微指摘件数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>不良指摘件数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未対応指摘件数</t>
         </is>
@@ -2812,30 +2925,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2854,27 +2972,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2882,9 +3000,14 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2895,7 +3018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2906,6 +3029,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2921,30 +3045,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>指摘件数</t>
+          <t>全指摘件数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>表示対象指摘件数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>指標対象指摘件数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>軽微指摘件数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>不良指摘件数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未対応指摘件数</t>
         </is>
@@ -2973,20 +3102,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3015,20 +3149,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3047,30 +3186,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3099,20 +3243,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3141,20 +3290,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3163,42 +3317,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>作業担当者</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>後工程</t>
+          <t>品質管理A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3210,35 +3369,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>品質管理A</t>
+          <t>品質管理B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3247,12 +3411,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>作業担当者</t>
+          <t>レビュー担当者</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>品質管理B</t>
+          <t>レビューリーダー乙</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3262,27 +3426,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3294,79 +3463,89 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>レビューリーダー乙</t>
+          <t>レビューリーダー甲</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>レビュー担当者</t>
+          <t>原因工程</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>レビューリーダー甲</t>
+          <t>コード</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3378,37 +3557,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>コード</t>
+          <t>テスト仕様書</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3420,37 +3604,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>内部仕様書</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3651,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>内部仕様書</t>
+          <t>外部仕様書</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3472,69 +3661,79 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>原因工程</t>
+          <t>検出工程</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>外部仕様書</t>
+          <t>コード</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3546,37 +3745,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>コード</t>
+          <t>テスト仕様書</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3588,35 +3792,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3630,37 +3839,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>リリース後</t>
+          <t>内部仕様書</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3886,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>内部仕様書</t>
+          <t>外部仕様書</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3682,116 +3896,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>検出工程</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>外部仕様書</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>検出工程</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>後工程</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:I19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4588,22 +4723,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4659,7 +4794,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>レビューリーダー甲</t>
+          <t>レビューリーダー乙</t>
         </is>
       </c>
     </row>
@@ -6072,22 +6207,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6143,7 +6278,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>レビューリーダー甲</t>
+          <t>レビューリーダー乙</t>
         </is>
       </c>
     </row>
@@ -6165,22 +6300,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>テスト仕様書</t>
+          <t>リリース後</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6236,7 +6371,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>レビューリーダー甲</t>
+          <t>レビューリーダー乙</t>
         </is>
       </c>
     </row>
